--- a/chicago/reference/resident-research/T-0509/T-0509_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0509/T-0509_resident_research_working.xlsx
@@ -692,12 +692,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>census_1840;census_1840_ruled;fergus_1839;fergus_1843;newberry_leads;norris_1844;old_settler_deaths;spend_crosswalk</t>
+          <t>census_1840;census_1840_ruled;fergus_1839;fergus_1843;newberry_leads;newspaper_register;norris_1844;old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>census_1840_ruled;fergus_1843;newberry_leads;norris_1844;spend_crosswalk</t>
+          <t>census_1840_ruled;fergus_1843;norris_1844;spend_crosswalk</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -822,12 +822,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -903,7 +903,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>fergus_1839_election;fergus_1843;newspaper_register;norris_1844;spend_crosswalk</t>
+          <t>fergus_1839_election;fergus_1843;newberry_leads;newspaper_register;norris_1844;spend_crosswalk</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>spend_crosswalk</t>
+          <t>address_backproj;fergus_1843;norris_1844;spend_crosswalk</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>fergus_1843;newberry_leads;norris_1844</t>
+          <t>fergus_1843;norris_1844</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>corroborated_enrichment</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>fergus_1839;fergus_1843;newberry_leads;newspaper_register;old_settler_deaths;spend_crosswalk</t>
+          <t>fergus_1839;fergus_1843;newberry_leads;newspaper_register;norris_1844;old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>fergus_1843;newberry_leads;spend_crosswalk</t>
+          <t>fergus_1843;newberry_leads;norris_1844;spend_crosswalk</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1950,12 +1950,12 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>no_corroboration</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>address_backproj;newberry_leads;old_settler_deaths;spend_crosswalk</t>
+          <t>address_backproj;old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>address_backproj;fergus_1839;fergus_1843;newberry_leads;newspaper_register;norris_1844;old_settler_deaths;spend_crosswalk</t>
+          <t>address_backproj;fergus_1839;fergus_1843;newspaper_register;norris_1844;old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>newberry_leads;spend_crosswalk</t>
+          <t>spend_crosswalk</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2583,12 +2583,12 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>corroborated_enrichment</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2749,12 +2749,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>fergus_1839;fergus_1843;newberry_leads;newspaper_register;spend_crosswalk</t>
+          <t>fergus_1839;fergus_1843;newberry_leads;newspaper_register</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>fergus_1843;newberry_leads;spend_crosswalk</t>
+          <t>fergus_1839;fergus_1843;newberry_leads</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>newberry_leads;newspaper_register;norris_1844</t>
+          <t>fergus_1843;newberry_leads;newspaper_register;norris_1844</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>norris_1844</t>
+          <t>fergus_1843;norris_1844</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Samuel Lewis is held as a candidate and not asserted: 6 Newberry genealogical-index card(s) stand under this surname on an exact-surname rule with nothing to separate the bearers; the census 1840 chicago familysearch images, chicago tribune 1882 04 25 old settler deaths agreement is a surname-only refusal; the papers carry the name 1834-07-02 to 1835-08-05, 1835-08-12 as schoolteacher.</t>
+          <t>Samuel Lewis is held as a candidate and not asserted: 1 Newberry genealogical-index card(s) stand under this surname on an exact-surname rule with nothing to separate the bearers; the census 1840 chicago familysearch images, chicago tribune 1882 04 25 old settler deaths agreement is a surname-only refusal; the papers carry the name 1834-07-02 to 1835-08-05, 1835-08-12 as schoolteacher.</t>
         </is>
       </c>
     </row>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3876,17 +3876,17 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>chicago_voter_lists_1833_1835_irad;encyclopedia_chicago_biographical_index_d</t>
+          <t>chicago_democrat_1833_1835;chicago_voter_lists_1833_1835_irad;encyclopedia_chicago_biographical_index_d</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>fergus_1839;fergus_1839_election;fergus_1843;newberry_leads;norris_1844;norris_adv;spend_crosswalk;voter_lists</t>
+          <t>address_backproj;census_1840;fergus_1839;fergus_1839_election;fergus_1843;newberry_leads;newspaper_register;norris_1844;norris_adv;spend_crosswalk;voter_lists</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>newberry_leads;norris_adv;spend_crosswalk</t>
+          <t>census_1840;newberry_leads;norris_adv;spend_crosswalk</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4007,18 +4007,18 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>no_corroboration</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>chicago_democrat_1833_1835</t>
+          <t>chicago_democrat_1833_1835;isa_public_domain_land_tract_sales</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -4445,12 +4445,12 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>fergus_1843;newberry_leads;newspaper_register;norris_1844</t>
+          <t>fergus_1843;newspaper_register;norris_1844</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>fergus_1843;newberry_leads;norris_1844</t>
+          <t>fergus_1843;norris_1844</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4591,12 +4591,12 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>fergus_1843;newberry_leads;newspaper_register;norris_1844;norris_adv;old_settler_deaths;spend_crosswalk</t>
+          <t>address_backproj;fergus_1843;newberry_leads;newspaper_register;norris_1844;norris_adv;old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>fergus_1843;norris_1844;norris_adv;old_settler_deaths;spend_crosswalk</t>
+          <t>address_backproj;fergus_1843;norris_1844;norris_adv;old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4724,12 +4724,12 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>chicago_voter_lists_1833_1835_irad;goodman_history_cook_county_early</t>
+          <t>chicago_democrat_1833_1835;chicago_voter_lists_1833_1835_irad;goodman_history_cook_county_early</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>fergus_1839;fergus_1839_election;fergus_1843;newberry_leads;norris_1844;spend_crosswalk;voter_lists</t>
+          <t>address_backproj;fergus_1839;fergus_1839_election;fergus_1843;newberry_leads;newspaper_register;norris_1844;spend_crosswalk;voter_lists</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>corroborated_enrichment</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>fergus_1843;newberry_leads;norris_1844;norris_adv;old_settler_deaths</t>
+          <t>fergus_1843;norris_1844;norris_adv;old_settler_deaths</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Rowland I!. Cook is held as a candidate and not asserted: 12 Newberry genealogical-index card(s) stand under this surname on an exact-surname rule with nothing to separate the bearers; the chicago tribune 1882 04 25 old settler deaths, fergus chicago directory 1843, newberry genealogical index, norris directory 1844 agreement is a surname-only refusal; the papers hold the name only on the post-office return(s) of 1834-04-16, 1835-07-01.</t>
+          <t>Rowland I!. Cook is held as a candidate and not asserted: 2 Newberry genealogical-index card(s) stand under this surname on an exact-surname rule with nothing to separate the bearers; the chicago tribune 1882 04 25 old settler deaths, fergus chicago directory 1843, norris directory 1844 agreement is a surname-only refusal; the papers hold the name only on the post-office return(s) of 1834-04-16, 1835-07-01.</t>
         </is>
       </c>
     </row>
@@ -5346,12 +5346,12 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Edward V Cooley is held as a candidate and not asserted: 4 Newberry genealogical-index card(s) stand under this surname on an exact-surname rule with nothing to separate the bearers; the fergus chicago directory 1843, norris directory 1844 agreement is a surname-only refusal; the papers hold the name only on the post-office return(s) of 1835-07-01.</t>
+          <t>Edward V Cooley is held as a candidate and not asserted: 3 Newberry genealogical-index card(s) stand under this surname on an exact-surname rule with nothing to separate the bearers; the fergus chicago directory 1843, norris directory 1844 agreement is a surname-only refusal; the papers hold the name only on the post-office return(s) of 1835-07-01.</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>newspaper_register</t>
+          <t>census_1840;newspaper_register</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -5564,17 +5564,17 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>chicago_voter_lists_1833_1835_irad;goodman_history_cook_county_hamilton</t>
+          <t>chicago_democrat_1833_1835;chicago_voter_lists_1833_1835_irad;goodman_history_cook_county_hamilton</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>fergus_1839;fergus_1843;newberry_leads;norris_1844;norris_adv;spend_crosswalk;voter_lists</t>
+          <t>address_backproj;fergus_1839;fergus_1843;newberry_leads;newspaper_register;norris_1844;norris_adv;spend_crosswalk;voter_lists</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>fergus_1843;norris_1844;norris_adv;spend_crosswalk</t>
+          <t>fergus_1839;fergus_1843;norris_1844;norris_adv;spend_crosswalk</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>fergus_1839_election;fergus_1843;newberry_leads;norris_1844;norris_adv;old_settler_deaths;spend_crosswalk;voter_lists</t>
+          <t>address_backproj;fergus_1839_election;fergus_1843;newberry_leads;newspaper_register;norris_1844;norris_adv;old_settler_deaths;spend_crosswalk;voter_lists</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>norris_1844;old_settler_deaths;spend_crosswalk</t>
+          <t>old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -6056,12 +6056,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -6472,12 +6472,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>corroborated_enrichment</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R3</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no_corroboration</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
     </row>
@@ -6856,12 +6856,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>corroborated_enrichment</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R3</t>
         </is>
       </c>
     </row>
@@ -7080,12 +7080,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7304,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -7368,12 +7368,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -7400,12 +7400,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -7496,12 +7496,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>no_corroboration</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R2</t>
         </is>
       </c>
     </row>
@@ -7656,12 +7656,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -7880,12 +7880,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>corroborated_enrichment</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R3</t>
         </is>
       </c>
     </row>
@@ -8104,12 +8104,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -8328,12 +8328,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8551,48 +8551,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Run with no arguments to write; `--check` re-derives and compares.</t>
+          <t>T-0816 READ THIS COHORT A SECOND TIME and ruled the 36 people the two readings</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>disagreed on.  Those rulings are evidence, not a hand edit of the output: they live in</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>32</v>
+          <t>data/research/residents/pass_14_reconciliation.json and this tool READS them, so the</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>8</v>
+          <t>ruled outcome and the discriminator that decided it re-derive like everything else.</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>corroborated_enrichment</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
+          <t>Fourteen of the 36 went against the mechanical rule below; the rule still produces what</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>T-0816 called the ledger of record, and the ruling is what is carried.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Run with no arguments to write; `--check` re-derives and compares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>candidate_identity</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>corroborated_enrichment</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>no_corroboration</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>22</v>
+      <c r="B44" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/chicago/reference/resident-research/T-0509/T-0509_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0509/T-0509_resident_research_working.xlsx
@@ -1330,7 +1330,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>address_backproj;fergus_1843;norris_1844;spend_crosswalk</t>
+          <t>address_backproj;fergus_1839;fergus_1843;norris_1844;spend_crosswalk</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>spend_crosswalk</t>
+          <t>fergus_1843;norris_1844;spend_crosswalk</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>spend_crosswalk</t>
+          <t>fergus_1839;spend_crosswalk</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>old_settler_deaths;spend_crosswalk</t>
+          <t>fergus_1843;old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">

--- a/chicago/reference/resident-research/T-0509/T-0509_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0509/T-0509_resident_research_working.xlsx
@@ -692,12 +692,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>census_1840;census_1840_ruled;fergus_1839;fergus_1843;newberry_leads;norris_1844;old_settler_deaths;spend_crosswalk</t>
+          <t>census_1840;census_1840_ruled;fergus_1839;fergus_1843;newberry_leads;newspaper_register;norris_1844;old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>census_1840_ruled;fergus_1843;newberry_leads;norris_1844;spend_crosswalk</t>
+          <t>census_1840_ruled;fergus_1843;norris_1844;spend_crosswalk</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -822,12 +822,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -903,7 +903,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>fergus_1839_election;fergus_1843;newspaper_register;norris_1844;spend_crosswalk</t>
+          <t>fergus_1839_election;fergus_1843;newberry_leads;newspaper_register;norris_1844;spend_crosswalk</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>spend_crosswalk</t>
+          <t>address_backproj;fergus_1839;fergus_1843;norris_1844;spend_crosswalk</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>fergus_1843;newberry_leads;norris_1844</t>
+          <t>fergus_1843;norris_1844</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1739,12 +1739,12 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>corroborated_enrichment</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>fergus_1839;fergus_1843;newberry_leads;newspaper_register;old_settler_deaths;spend_crosswalk</t>
+          <t>fergus_1839;fergus_1843;newberry_leads;newspaper_register;norris_1844;old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>fergus_1843;newberry_leads;spend_crosswalk</t>
+          <t>fergus_1843;newberry_leads;norris_1844;spend_crosswalk</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1950,12 +1950,12 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>no_corroboration</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>address_backproj;newberry_leads;old_settler_deaths;spend_crosswalk</t>
+          <t>address_backproj;old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>address_backproj;fergus_1839;fergus_1843;newberry_leads;newspaper_register;norris_1844;old_settler_deaths;spend_crosswalk</t>
+          <t>address_backproj;fergus_1839;fergus_1843;newspaper_register;norris_1844;old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>newberry_leads;spend_crosswalk</t>
+          <t>spend_crosswalk</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2583,12 +2583,12 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>corroborated_enrichment</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>spend_crosswalk</t>
+          <t>fergus_1843;norris_1844;spend_crosswalk</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>fergus_1839;fergus_1843;newberry_leads;newspaper_register;spend_crosswalk</t>
+          <t>fergus_1839;fergus_1843;newberry_leads;newspaper_register</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>fergus_1843;newberry_leads;spend_crosswalk</t>
+          <t>fergus_1839;fergus_1843;newberry_leads</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>newberry_leads;newspaper_register;norris_1844</t>
+          <t>fergus_1843;newberry_leads;newspaper_register;norris_1844</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>norris_1844</t>
+          <t>fergus_1843;norris_1844</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Samuel Lewis is held as a candidate and not asserted: 6 Newberry genealogical-index card(s) stand under this surname on an exact-surname rule with nothing to separate the bearers; the census 1840 chicago familysearch images, chicago tribune 1882 04 25 old settler deaths agreement is a surname-only refusal; the papers carry the name 1834-07-02 to 1835-08-05, 1835-08-12 as schoolteacher.</t>
+          <t>Samuel Lewis is held as a candidate and not asserted: 1 Newberry genealogical-index card(s) stand under this surname on an exact-surname rule with nothing to separate the bearers; the census 1840 chicago familysearch images, chicago tribune 1882 04 25 old settler deaths agreement is a surname-only refusal; the papers carry the name 1834-07-02 to 1835-08-05, 1835-08-12 as schoolteacher.</t>
         </is>
       </c>
     </row>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3876,17 +3876,17 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>chicago_voter_lists_1833_1835_irad;encyclopedia_chicago_biographical_index_d</t>
+          <t>chicago_democrat_1833_1835;chicago_voter_lists_1833_1835_irad;encyclopedia_chicago_biographical_index_d</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>fergus_1839;fergus_1839_election;fergus_1843;newberry_leads;norris_1844;norris_adv;spend_crosswalk;voter_lists</t>
+          <t>address_backproj;census_1840;fergus_1839;fergus_1839_election;fergus_1843;newberry_leads;newspaper_register;norris_1844;norris_adv;spend_crosswalk;voter_lists</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>newberry_leads;norris_adv;spend_crosswalk</t>
+          <t>census_1840;newberry_leads;norris_adv;spend_crosswalk</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4007,18 +4007,18 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>no_corroboration</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>chicago_democrat_1833_1835</t>
+          <t>chicago_democrat_1833_1835;isa_public_domain_land_tract_sales</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -4445,12 +4445,12 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>fergus_1843;newberry_leads;newspaper_register;norris_1844</t>
+          <t>fergus_1843;newspaper_register;norris_1844</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>fergus_1843;newberry_leads;norris_1844</t>
+          <t>fergus_1843;norris_1844</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>spend_crosswalk</t>
+          <t>fergus_1839;spend_crosswalk</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4591,12 +4591,12 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>fergus_1843;newberry_leads;newspaper_register;norris_1844;norris_adv;old_settler_deaths;spend_crosswalk</t>
+          <t>address_backproj;fergus_1843;newberry_leads;newspaper_register;norris_1844;norris_adv;old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>fergus_1843;norris_1844;norris_adv;old_settler_deaths;spend_crosswalk</t>
+          <t>address_backproj;fergus_1843;norris_1844;norris_adv;old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4724,12 +4724,12 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>chicago_voter_lists_1833_1835_irad;goodman_history_cook_county_early</t>
+          <t>chicago_democrat_1833_1835;chicago_voter_lists_1833_1835_irad;goodman_history_cook_county_early</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>fergus_1839;fergus_1839_election;fergus_1843;newberry_leads;norris_1844;spend_crosswalk;voter_lists</t>
+          <t>address_backproj;fergus_1839;fergus_1839_election;fergus_1843;newberry_leads;newspaper_register;norris_1844;spend_crosswalk;voter_lists</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>corroborated_enrichment</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>old_settler_deaths;spend_crosswalk</t>
+          <t>fergus_1843;old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>fergus_1843;newberry_leads;norris_1844;norris_adv;old_settler_deaths</t>
+          <t>fergus_1843;norris_1844;norris_adv;old_settler_deaths</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Rowland I!. Cook is held as a candidate and not asserted: 12 Newberry genealogical-index card(s) stand under this surname on an exact-surname rule with nothing to separate the bearers; the chicago tribune 1882 04 25 old settler deaths, fergus chicago directory 1843, newberry genealogical index, norris directory 1844 agreement is a surname-only refusal; the papers hold the name only on the post-office return(s) of 1834-04-16, 1835-07-01.</t>
+          <t>Rowland I!. Cook is held as a candidate and not asserted: 2 Newberry genealogical-index card(s) stand under this surname on an exact-surname rule with nothing to separate the bearers; the chicago tribune 1882 04 25 old settler deaths, fergus chicago directory 1843, norris directory 1844 agreement is a surname-only refusal; the papers hold the name only on the post-office return(s) of 1834-04-16, 1835-07-01.</t>
         </is>
       </c>
     </row>
@@ -5346,12 +5346,12 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Edward V Cooley is held as a candidate and not asserted: 4 Newberry genealogical-index card(s) stand under this surname on an exact-surname rule with nothing to separate the bearers; the fergus chicago directory 1843, norris directory 1844 agreement is a surname-only refusal; the papers hold the name only on the post-office return(s) of 1835-07-01.</t>
+          <t>Edward V Cooley is held as a candidate and not asserted: 3 Newberry genealogical-index card(s) stand under this surname on an exact-surname rule with nothing to separate the bearers; the fergus chicago directory 1843, norris directory 1844 agreement is a surname-only refusal; the papers hold the name only on the post-office return(s) of 1835-07-01.</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>newspaper_register</t>
+          <t>census_1840;newspaper_register</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -5564,17 +5564,17 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>chicago_voter_lists_1833_1835_irad;goodman_history_cook_county_hamilton</t>
+          <t>chicago_democrat_1833_1835;chicago_voter_lists_1833_1835_irad;goodman_history_cook_county_hamilton</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>fergus_1839;fergus_1843;newberry_leads;norris_1844;norris_adv;spend_crosswalk;voter_lists</t>
+          <t>address_backproj;fergus_1839;fergus_1843;newberry_leads;newspaper_register;norris_1844;norris_adv;spend_crosswalk;voter_lists</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>fergus_1843;norris_1844;norris_adv;spend_crosswalk</t>
+          <t>fergus_1839;fergus_1843;norris_1844;norris_adv;spend_crosswalk</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>fergus_1839_election;fergus_1843;newberry_leads;norris_1844;norris_adv;old_settler_deaths;spend_crosswalk;voter_lists</t>
+          <t>address_backproj;fergus_1839_election;fergus_1843;newberry_leads;newspaper_register;norris_1844;norris_adv;old_settler_deaths;spend_crosswalk;voter_lists</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>norris_1844;old_settler_deaths;spend_crosswalk</t>
+          <t>old_settler_deaths;spend_crosswalk</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -6056,12 +6056,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6344,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -6472,12 +6472,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>corroborated_enrichment</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R3</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no_corroboration</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
     </row>
@@ -6856,12 +6856,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>corroborated_enrichment</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R3</t>
         </is>
       </c>
     </row>
@@ -7080,12 +7080,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7304,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -7368,12 +7368,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -7400,12 +7400,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -7496,12 +7496,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>no_corroboration</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R2</t>
         </is>
       </c>
     </row>
@@ -7656,12 +7656,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -7880,12 +7880,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>corroborated_enrichment</t>
+          <t>candidate_identity</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R3</t>
         </is>
       </c>
     </row>
@@ -8104,12 +8104,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -8328,12 +8328,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
+          <t>no_corroboration</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8551,48 +8551,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Run with no arguments to write; `--check` re-derives and compares.</t>
+          <t>T-0816 READ THIS COHORT A SECOND TIME and ruled the 36 people the two readings</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>disagreed on.  Those rulings are evidence, not a hand edit of the output: they live in</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>candidate_identity</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>32</v>
+          <t>data/research/residents/pass_14_reconciliation.json and this tool READS them, so the</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>8</v>
+          <t>ruled outcome and the discriminator that decided it re-derive like everything else.</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>corroborated_enrichment</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>14</v>
+          <t>Fourteen of the 36 went against the mechanical rule below; the rule still produces what</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>T-0816 called the ledger of record, and the ruling is what is carried.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Run with no arguments to write; `--check` re-derives and compares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>candidate_identity</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>corroborated_enrichment</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>no_corroboration</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>22</v>
+      <c r="B44" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
